--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92570332695</v>
+        <v>46157.93105367703</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105367703</v>
+        <v>46157.93176419771</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93176419771</v>
+        <v>46157.93401744743</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401744743</v>
+        <v>46157.93719791132</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719791132</v>
+        <v>46158.28217865348</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217865348</v>
+        <v>46158.29685417671</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29685417671</v>
+        <v>46158.2981684183</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981684183</v>
+        <v>46158.33388985684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388985684</v>
+        <v>46158.36858722843</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858722843</v>
+        <v>46158.37289443414</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
